--- a/public/mau-import-phan-bo.xlsx
+++ b/public/mau-import-phan-bo.xlsx
@@ -425,7 +425,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>VG1246060108</v>
+        <v>AZ1664430120-SMS-30759</v>
       </c>
       <c r="B2" t="str">
         <v>OWN-2610-0001</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>611600080113</v>
+        <v>AZ1664440069-SMS-30705</v>
       </c>
       <c r="B3" t="str">
         <v>OWN-2610-0002</v>
